--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_metropolitana.xlsx
@@ -171,7 +171,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:44</t>
+    <t xml:space="preserve">2026-09-09 20:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2022_metropolitana.xlsx
@@ -24,144 +24,144 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conchalí</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
-    <t xml:space="preserve">El Bosque</t>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
   </si>
   <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Espejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -171,7 +171,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:49</t>
+    <t xml:space="preserve">2026-09-18 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -583,7 +583,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.78</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.37</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="5">
@@ -607,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.89</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="6">
@@ -615,7 +615,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.06</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="7">
@@ -623,7 +623,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +631,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.17</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="9">
@@ -639,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.94</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="10">
@@ -647,7 +647,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -655,7 +655,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
@@ -663,7 +663,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.41</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="13">
@@ -671,7 +671,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.83</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="14">
@@ -679,7 +679,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.82</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="15">
@@ -687,7 +687,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.77</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="16">
@@ -695,7 +695,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.32</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="18">
@@ -711,7 +711,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="19">
@@ -719,7 +719,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="20">
@@ -727,7 +727,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.14</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="21">
@@ -735,7 +735,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.47</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="22">
@@ -743,7 +743,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>3.57</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="23">
@@ -751,7 +751,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>3.11</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="24">
@@ -759,7 +759,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2.51</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="25">
@@ -767,7 +767,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2.38</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="26">
@@ -775,7 +775,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="27">
@@ -783,7 +783,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="28">
@@ -791,7 +791,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.22</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="29">
@@ -799,7 +799,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="30">
@@ -807,7 +807,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2.69</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="31">
@@ -815,7 +815,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="32">
@@ -823,7 +823,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.91</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="33">
@@ -831,7 +831,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="34">
@@ -839,7 +839,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1.86</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="35">
@@ -847,7 +847,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.87</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="36">
@@ -855,7 +855,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2.34</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="37">
@@ -863,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>3.18</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="38">
@@ -871,7 +871,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="39">
@@ -879,7 +879,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>3.14</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="40">
@@ -887,7 +887,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2.82</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="41">
@@ -895,7 +895,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2.99</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="42">
@@ -903,7 +903,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2.81</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="43">
@@ -911,7 +911,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="44">
@@ -919,7 +919,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="45">
@@ -927,7 +927,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="46">
@@ -935,7 +935,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="47">
@@ -943,7 +943,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.71</v>
+        <v>1.91</v>
       </c>
     </row>
   </sheetData>
